--- a/data/trans_camb/P16A11-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P16A11-Edad-trans_camb.xlsx
@@ -677,17 +677,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,32; 0,74</t>
+          <t>-0,31; 0,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 0,0</t>
+          <t>-0,64; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 0,08</t>
+          <t>-0,79; 0,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -697,27 +697,27 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,15</t>
+          <t>0,0; 1,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,55</t>
+          <t>0,0; 2,84</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 0,54</t>
+          <t>-0,16; 0,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 0,37</t>
+          <t>-0,16; 0,44</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 1,18</t>
+          <t>-0,12; 1,27</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,05; 1,86</t>
+          <t>0,05; 1,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 1,85</t>
+          <t>0,05; 2,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 1,27</t>
+          <t>-0,36; 1,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 2,14</t>
+          <t>-0,45; 2,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 0,37</t>
+          <t>-1,28; 0,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 1,39</t>
+          <t>-0,8; 1,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,07; 1,57</t>
+          <t>0,05; 1,55</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 0,85</t>
+          <t>-0,36; 0,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,96</t>
+          <t>-0,3; 1,02</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-59,92; —</t>
+          <t>-41,56; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-52,76; 798,34</t>
+          <t>-49,53; 718,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1024,22 +1024,22 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-78,93; 511,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 642,76</t>
+          <t>-2,42; 592,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-62,7; 408,41</t>
+          <t>-60,58; 358,85</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-64,73; 367,79</t>
+          <t>-61,09; 408,97</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 4,18</t>
+          <t>-0,07; 4,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 2,54</t>
+          <t>-1,29; 2,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 3,1</t>
+          <t>-1,08; 2,88</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 0,95</t>
+          <t>-3,03; 0,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,73; -0,03</t>
+          <t>-3,83; 0,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,16; -0,47</t>
+          <t>-4,07; -0,58</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 2,03</t>
+          <t>-1,01; 1,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 0,7</t>
+          <t>-2,04; 0,67</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 0,67</t>
+          <t>-2,07; 0,68</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 232,42</t>
+          <t>-4,96; 240,4</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-35,53; 158,3</t>
+          <t>-38,44; 152,82</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-31,76; 179,37</t>
+          <t>-34,97; 156,66</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-57,13; 31,98</t>
+          <t>-58,02; 32,61</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-70,01; 3,38</t>
+          <t>-71,88; 8,02</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-73,91; -10,23</t>
+          <t>-76,27; -15,76</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-23,88; 76,22</t>
+          <t>-25,75; 72,71</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-49,08; 28,96</t>
+          <t>-49,0; 27,07</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-50,08; 24,8</t>
+          <t>-48,88; 26,89</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 3,25</t>
+          <t>-4,93; 2,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 4,99</t>
+          <t>-3,19; 5,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,81; 3,55</t>
+          <t>-9,66; 3,27</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 6,47</t>
+          <t>-1,25; 6,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 2,37</t>
+          <t>-4,68; 2,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 5,0</t>
+          <t>-2,23; 5,15</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 3,65</t>
+          <t>-2,24; 3,4</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 2,59</t>
+          <t>-2,8; 2,52</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,51; 3,0</t>
+          <t>-5,75; 3,08</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-33,42; 31,95</t>
+          <t>-33,98; 29,05</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-21,78; 46,81</t>
+          <t>-21,05; 47,94</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-64,75; 29,8</t>
+          <t>-67,05; 27,23</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-8,82; 74,21</t>
+          <t>-11,67; 78,97</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-37,59; 29,47</t>
+          <t>-38,48; 24,59</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-18,13; 59,13</t>
+          <t>-17,25; 58,34</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-14,46; 35,95</t>
+          <t>-17,28; 33,31</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-22,2; 25,58</t>
+          <t>-21,71; 24,23</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-40,94; 27,59</t>
+          <t>-43,13; 27,9</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 11,71</t>
+          <t>-1,65; 11,57</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-13,84; -1,73</t>
+          <t>-14,41; -1,93</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 3,74</t>
+          <t>-8,09; 3,4</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,27; 13,68</t>
+          <t>1,38; 14,32</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 4,44</t>
+          <t>-8,76; 4,16</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-12,59; -1,92</t>
+          <t>-12,95; -2,06</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,7; 11,06</t>
+          <t>1,85; 11,22</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-9,44; -0,25</t>
+          <t>-9,44; -0,78</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-8,55; -0,53</t>
+          <t>-8,51; -0,64</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 42,73</t>
+          <t>-5,07; 41,6</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-41,17; -5,68</t>
+          <t>-42,26; -7,14</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-22,92; 13,7</t>
+          <t>-23,98; 12,7</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>0,48; 46,44</t>
+          <t>3,69; 49,86</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-24,14; 14,83</t>
+          <t>-25,33; 14,23</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-35,19; -6,76</t>
+          <t>-35,43; -7,11</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,1; 39,24</t>
+          <t>5,32; 39,15</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-28,23; -0,89</t>
+          <t>-28,21; -2,84</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-25,21; -1,93</t>
+          <t>-24,98; -2,33</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>4,43; 20,93</t>
+          <t>4,75; 21,09</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 10,86</t>
+          <t>-4,41; 10,95</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1,81; 15,62</t>
+          <t>1,3; 15,5</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3,47; 18,42</t>
+          <t>3,31; 19,08</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-7,65; 6,41</t>
+          <t>-7,42; 7,32</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 43,02</t>
+          <t>-2,58; 39,55</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,08; 17,29</t>
+          <t>6,46; 17,12</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 6,25</t>
+          <t>-3,66; 6,45</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2,75; 36,63</t>
+          <t>3,11; 37,04</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>10,15; 59,85</t>
+          <t>11,55; 60,65</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-11,42; 31,77</t>
+          <t>-10,14; 31,43</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>4,13; 45,68</t>
+          <t>3,61; 45,7</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>7,17; 43,96</t>
+          <t>6,34; 45,14</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-15,35; 14,92</t>
+          <t>-15,1; 17,69</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 110,43</t>
+          <t>-5,41; 95,94</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>13,38; 43,22</t>
+          <t>13,82; 42,69</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-10,12; 16,08</t>
+          <t>-8,09; 16,05</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>6,38; 92,27</t>
+          <t>7,6; 92,68</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>3,18; 21,88</t>
+          <t>2,83; 22,43</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 16,49</t>
+          <t>-1,01; 16,45</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2,87; 19,19</t>
+          <t>2,43; 18,9</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,72; 15,44</t>
+          <t>0,83; 16,54</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 9,17</t>
+          <t>-6,41; 9,52</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,03; 15,38</t>
+          <t>2,33; 14,96</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,31; 16,45</t>
+          <t>4,03; 16,28</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 9,27</t>
+          <t>-2,49; 9,43</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3,99; 14,58</t>
+          <t>4,52; 14,49</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>6,03; 52,65</t>
+          <t>5,13; 53,09</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 38,95</t>
+          <t>-2,1; 39,44</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>5,37; 46,62</t>
+          <t>4,51; 45,05</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1,21; 30,39</t>
+          <t>1,38; 32,68</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-11,32; 18,13</t>
+          <t>-10,41; 18,84</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,37; 30,82</t>
+          <t>3,97; 29,39</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,78; 33,31</t>
+          <t>7,24; 33,82</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 18,55</t>
+          <t>-4,5; 19,24</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>7,09; 29,97</t>
+          <t>7,89; 29,69</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2,23; 5,78</t>
+          <t>2,4; 5,79</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,95</t>
+          <t>0,6; 3,95</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1,01; 7,31</t>
+          <t>1,29; 7,11</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2,51; 6,17</t>
+          <t>2,32; 6,05</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 2,84</t>
+          <t>-0,78; 2,94</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2,9; 22,26</t>
+          <t>2,81; 20,6</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,87; 5,4</t>
+          <t>2,89; 5,53</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0,37; 2,99</t>
+          <t>0,35; 2,84</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3,66; 15,42</t>
+          <t>3,64; 16,87</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>16,44; 48,97</t>
+          <t>17,27; 48,24</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>4,64; 33,87</t>
+          <t>4,52; 33,01</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>9,22; 60,54</t>
+          <t>11,63; 58,49</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>14,19; 39,59</t>
+          <t>13,53; 38,73</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 18,31</t>
+          <t>-4,44; 18,79</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>17,27; 129,5</t>
+          <t>16,33; 128,3</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>18,59; 38,31</t>
+          <t>18,72; 39,13</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>2,54; 21,34</t>
+          <t>2,43; 20,28</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>24,12; 103,79</t>
+          <t>24,26; 116,96</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A11-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P16A11-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,12</t>
+          <t>0,54</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,52</t>
+          <t>0,56</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,17</t>
+          <t>0,55</t>
         </is>
       </c>
     </row>
@@ -677,17 +677,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 0,72</t>
+          <t>-0,32; 0,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 0,0</t>
+          <t>-0,8; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 0,08</t>
+          <t>-0,22; 3,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -702,22 +702,22 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,84</t>
+          <t>0,0; 2,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 0,35</t>
+          <t>-0,16; 0,44</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 0,44</t>
+          <t>-0,16; 0,37</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 1,27</t>
+          <t>0,0; 1,91</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-73,23%</t>
+          <t>340,28%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>209,22%</t>
+          <t>678,69%</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>0,21</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>0,21</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,05; 1,9</t>
+          <t>0,06; 1,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,05; 2,01</t>
+          <t>-0,03; 1,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 1,41</t>
+          <t>-0,36; 1,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 2,13</t>
+          <t>-0,56; 2,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 0,37</t>
+          <t>-1,35; 0,34</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 1,36</t>
+          <t>-0,85; 1,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,05; 1,55</t>
+          <t>0,03; 1,67</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 0,9</t>
+          <t>-0,4; 0,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 1,02</t>
+          <t>-0,36; 0,88</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>43,31%</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-41,56; —</t>
+          <t>-57,69; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1014,32 +1014,32 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-49,53; 718,41</t>
+          <t>-70,61; 564,22</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 262,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-77,58; 497,11</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-2,42; 592,16</t>
+          <t>-10,06; 584,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-60,58; 358,85</t>
+          <t>-58,47; 352,3</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-61,09; 408,97</t>
+          <t>-60,1; 377,12</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,99</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-2,17</t>
+          <t>-2,15</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,69</t>
+          <t>-0,61</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 4,14</t>
+          <t>-0,08; 4,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 2,55</t>
+          <t>-1,22; 2,48</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 2,88</t>
+          <t>-0,88; 3,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 0,96</t>
+          <t>-3,07; 1,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,83; 0,21</t>
+          <t>-3,63; 0,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-4,07; -0,58</t>
+          <t>-4,08; -0,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 1,96</t>
+          <t>-1,07; 1,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 0,67</t>
+          <t>-2,09; 0,54</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 0,68</t>
+          <t>-1,95; 0,79</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>38,04%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-51,95%</t>
+          <t>-51,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-20,2%</t>
+          <t>-17,83%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 240,4</t>
+          <t>-4,54; 225,28</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-38,44; 152,82</t>
+          <t>-40,5; 134,72</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-34,97; 156,66</t>
+          <t>-30,27; 171,3</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-58,02; 32,61</t>
+          <t>-56,18; 31,01</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-71,88; 8,02</t>
+          <t>-68,9; 17,73</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-76,27; -15,76</t>
+          <t>-73,1; -11,03</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-25,75; 72,71</t>
+          <t>-26,33; 69,6</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-49,0; 27,07</t>
+          <t>-49,71; 19,85</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-48,88; 26,89</t>
+          <t>-48,46; 28,43</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-2,0</t>
+          <t>1,32</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,37</t>
+          <t>1,57</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,39</t>
+          <t>1,41</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 2,98</t>
+          <t>-4,75; 2,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,19; 5,1</t>
+          <t>-3,04; 4,96</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-9,66; 3,27</t>
+          <t>-2,51; 5,18</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 6,62</t>
+          <t>-1,02; 6,77</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 2,15</t>
+          <t>-4,54; 2,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 5,15</t>
+          <t>-1,72; 4,76</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 3,4</t>
+          <t>-1,74; 3,66</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 2,52</t>
+          <t>-2,7; 2,66</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 3,08</t>
+          <t>-1,06; 4,26</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-15,7%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-3,31%</t>
+          <t>12,12%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-33,98; 29,05</t>
+          <t>-32,49; 26,27</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-21,05; 47,94</t>
+          <t>-20,97; 46,94</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-67,05; 27,23</t>
+          <t>-17,37; 48,56</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-11,67; 78,97</t>
+          <t>-8,03; 76,56</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-38,48; 24,59</t>
+          <t>-36,03; 27,98</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-17,25; 58,34</t>
+          <t>-13,96; 55,45</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-17,28; 33,31</t>
+          <t>-13,82; 35,54</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-21,71; 24,23</t>
+          <t>-20,79; 25,38</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-43,13; 27,9</t>
+          <t>-8,49; 42,16</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-1,98</t>
+          <t>-2,59</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-7,17</t>
+          <t>-6,62</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-4,57</t>
+          <t>-4,63</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 11,57</t>
+          <t>-1,78; 11,92</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-14,41; -1,93</t>
+          <t>-14,02; -1,49</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 3,4</t>
+          <t>-8,07; 2,54</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,38; 14,32</t>
+          <t>0,87; 14,11</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,76; 4,16</t>
+          <t>-8,06; 3,98</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-12,95; -2,06</t>
+          <t>-11,56; -1,27</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,85; 11,22</t>
+          <t>1,42; 11,01</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-9,44; -0,78</t>
+          <t>-9,79; -1,08</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-8,51; -0,64</t>
+          <t>-8,58; -0,92</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-6,52%</t>
+          <t>-8,54%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-22,16%</t>
+          <t>-20,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-14,59%</t>
+          <t>-14,75%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 41,6</t>
+          <t>-5,39; 43,99</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-42,26; -7,14</t>
+          <t>-41,96; -5,18</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-23,98; 12,7</t>
+          <t>-24,09; 9,23</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3,69; 49,86</t>
+          <t>3,09; 49,17</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-25,33; 14,23</t>
+          <t>-22,47; 13,71</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-35,43; -7,11</t>
+          <t>-32,28; -4,42</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>5,32; 39,15</t>
+          <t>4,2; 38,24</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-28,21; -2,84</t>
+          <t>-28,77; -3,48</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-24,98; -2,33</t>
+          <t>-25,36; -3,13</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>9,32</t>
+          <t>8,36</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>17,99</t>
+          <t>0,29</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>15,34</t>
+          <t>4,02</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>4,75; 21,09</t>
+          <t>4,24; 20,77</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 10,95</t>
+          <t>-3,97; 11,14</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1,3; 15,5</t>
+          <t>1,45; 15,19</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>3,31; 19,08</t>
+          <t>3,46; 18,04</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-7,42; 7,32</t>
+          <t>-7,32; 6,63</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 39,55</t>
+          <t>-5,31; 5,98</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,46; 17,12</t>
+          <t>6,05; 16,81</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 6,45</t>
+          <t>-4,41; 6,77</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>3,11; 37,04</t>
+          <t>-0,57; 8,28</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>39,28%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>11,55; 60,65</t>
+          <t>10,06; 60,28</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-10,14; 31,43</t>
+          <t>-9,8; 32,79</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>3,61; 45,7</t>
+          <t>3,26; 44,46</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>6,34; 45,14</t>
+          <t>6,73; 43,43</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-15,1; 17,69</t>
+          <t>-15,09; 15,32</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 95,94</t>
+          <t>-10,76; 14,39</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>13,82; 42,69</t>
+          <t>13,62; 42,78</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 16,05</t>
+          <t>-9,76; 17,34</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>7,6; 92,68</t>
+          <t>-1,31; 21,11</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>10,74</t>
+          <t>10,59</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,58</t>
+          <t>8,31</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>9,32</t>
+          <t>9,09</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>2,83; 22,43</t>
+          <t>3,54; 22,72</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 16,45</t>
+          <t>-1,57; 17,07</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2,43; 18,9</t>
+          <t>2,93; 19,21</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,83; 16,54</t>
+          <t>1,16; 16,4</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 9,52</t>
+          <t>-7,17; 8,95</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,33; 14,96</t>
+          <t>1,35; 14,49</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,03; 16,28</t>
+          <t>4,15; 16,0</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 9,43</t>
+          <t>-2,75; 9,55</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>4,52; 14,49</t>
+          <t>4,19; 14,37</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,29%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>5,13; 53,09</t>
+          <t>6,69; 53,77</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 39,44</t>
+          <t>-3,18; 42,15</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>4,51; 45,05</t>
+          <t>5,39; 46,33</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1,38; 32,68</t>
+          <t>2,03; 31,73</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-10,41; 18,84</t>
+          <t>-12,15; 17,72</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,97; 29,39</t>
+          <t>2,36; 28,14</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,24; 33,82</t>
+          <t>7,32; 32,16</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 19,24</t>
+          <t>-4,73; 19,34</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>7,89; 29,69</t>
+          <t>7,42; 29,36</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>5,11</t>
+          <t>6,15</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>8,0</t>
+          <t>3,86</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>6,62</t>
+          <t>5,0</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2,4; 5,79</t>
+          <t>2,32; 5,72</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>0,6; 3,95</t>
+          <t>0,48; 3,78</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>1,29; 7,11</t>
+          <t>4,5; 7,94</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>2,32; 6,05</t>
+          <t>2,29; 6,18</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 2,94</t>
+          <t>-0,86; 2,9</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>2,81; 20,6</t>
+          <t>2,37; 5,44</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>2,89; 5,53</t>
+          <t>2,83; 5,49</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,84</t>
+          <t>0,34; 2,99</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>3,64; 16,87</t>
+          <t>3,76; 6,2</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>48,74%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>34,04%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>17,27; 48,24</t>
+          <t>16,86; 48,05</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>4,52; 33,01</t>
+          <t>3,62; 31,9</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>11,63; 58,49</t>
+          <t>32,88; 66,97</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>13,53; 38,73</t>
+          <t>12,75; 38,66</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 18,79</t>
+          <t>-4,96; 18,49</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>16,33; 128,3</t>
+          <t>13,31; 34,9</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>18,72; 39,13</t>
+          <t>18,51; 38,89</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>2,43; 20,28</t>
+          <t>2,18; 21,44</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>24,26; 116,96</t>
+          <t>24,8; 44,47</t>
         </is>
       </c>
     </row>
